--- a/internal_doc/05.测试设计/story/sequoiafs/目录及文件操作.xlsx
+++ b/internal_doc/05.测试设计/story/sequoiafs/目录及文件操作.xlsx
@@ -7,8 +7,8 @@
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="文件及目录操作" sheetId="1" r:id="rId1"/>
+    <sheet name="新增接口验证" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="170">
   <si>
     <t>测试点</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -369,6 +369,374 @@
   </si>
   <si>
     <t>全部lob数据、部分lob数据、不存在的lob数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接口名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chmod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fcntl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mknod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mmap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>openat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>socket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>umask</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>close</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>link</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lseek</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>read</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unlink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>write</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fopen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fifo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>path_resolution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>symlink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关联接口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>open</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duplicate a file descriptor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dup2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dup3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int dup2(int oldfd, int newfd)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int dup3(int oldfd, int newfd, int flags)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int dup(int oldfd)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fclose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shutdown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lockf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>capabilities</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feature_test_macros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int link(const char *oldpath, const char *newpath)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linkat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rename</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ln</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int fcntl(int fd, int cmd, ... /* arg */ )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create a special or ordinary file</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int mknod(const char *pathname, mode_t mode, dev_t dev)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fseek</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lseek64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>posix_fallocate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reposition read/write file offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>off_t lseek(int fd, off_t offset, int whence)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manipulate file descriptor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>make a new name for a file</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map or unmap files or devices into memory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int munmap(void *addr, size_t length)
+void *mmap(void *addr, size_t length, int prot, int flags,
+                  int fd, off_t offset)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>open a file relative to a directory file descriptor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int openat(int dirfd, const char *pathname, int flags)
+int openat(int dirfd, const char *pathname, int flags, mode_t mode)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ssize_t read(int fd, void *buf, size_t count)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>read from a file descriptor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ioctl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>readdir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>readlink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>readv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不涉及</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get file status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int stat(const char *path, struct stat *buf)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int fstat(int fd, struct stat *buf)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int lstat(const char *path, struct stat *buf)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fstat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lstat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set file mode creation mask</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mode_t umask(mode_t mask)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int unlink(const char *pathname)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rmdir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unlinkat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mkfifo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ssize_t write(int fd, const void *buf, size_t count)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>write to a file descriptor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsync</t>
+  </si>
+  <si>
+    <t>pwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>writev</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FILE *fopen(const char *path, const char *mode)
+FILE *fdopen(int fd, const char *mode)
+FILE *freopen(const char *path, const char *mode, FILE *stream)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fileno</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fmemopen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fopencookie</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -412,11 +780,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -973,7 +1345,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="40.5">
@@ -984,7 +1356,7 @@
         <v>37</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="40.5">
@@ -995,7 +1367,7 @@
         <v>38</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="54">
@@ -1256,11 +1628,504 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="21.75" customWidth="1"/>
+    <col min="3" max="3" width="61.125" customWidth="1"/>
+    <col min="4" max="4" width="53.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2"/>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2"/>
+      <c r="B4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2"/>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2"/>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2"/>
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2"/>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2"/>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2"/>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2"/>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="40.5">
+      <c r="A12" s="2"/>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2"/>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="40.5">
+      <c r="A14" s="2"/>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2"/>
+      <c r="B15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2"/>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2"/>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2"/>
+      <c r="B18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2"/>
+      <c r="B19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2"/>
+      <c r="B20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2"/>
+      <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2"/>
+      <c r="B22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="54">
+      <c r="A23" s="2"/>
+      <c r="B23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2"/>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2"/>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2"/>
+      <c r="B26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="3"/>
+      <c r="B28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="3"/>
+      <c r="B30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="3"/>
+      <c r="B31" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="3"/>
+      <c r="B32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="3"/>
+      <c r="B34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="3"/>
+      <c r="B35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="3"/>
+      <c r="B36" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3"/>
+      <c r="B37" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3"/>
+      <c r="B38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3"/>
+      <c r="B40" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3"/>
+      <c r="B41" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3"/>
+      <c r="B42" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="B44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="B45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="B46" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="B47" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="B48" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="B49" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="B50" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="B52" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="B53" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="B54" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="B55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="B57" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="B58" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="B59" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>98</v>
+      </c>
+      <c r="B60" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="B61" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="B62" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:A26"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="D17:D19"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
